--- a/docs/operadoras/larissa/Contatos-Clientes-Larissa VALIDADO.xlsx
+++ b/docs/operadoras/larissa/Contatos-Clientes-Larissa VALIDADO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/caiodevasconcelos/Documents/:code:cockpit-v2 /cockpit-v2-starter/docs/operadoras/larissa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D857E116-0DFD-7B48-BBD9-FBB88AFF88BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F07D86E-EE9C-5645-938D-A1147028EE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16820" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INSTRUÇÕES" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="184">
   <si>
     <t>Cockpit Sal Express — Planilha de Cadastro de Clientes e Contatos</t>
   </si>
@@ -575,6 +575,30 @@
   <si>
     <t>INOVAMED</t>
   </si>
+  <si>
+    <t>SIRIO PHARMA LTDA</t>
+  </si>
+  <si>
+    <t>SIRI3149</t>
+  </si>
+  <si>
+    <t>recebimento@siriopharma.com.br</t>
+  </si>
+  <si>
+    <t>farmaceutica@siriopharma.com.br</t>
+  </si>
+  <si>
+    <t>logistica@siriopharma.com.br</t>
+  </si>
+  <si>
+    <t>comercial2@lifenutri.com.br</t>
+  </si>
+  <si>
+    <t>LEONE</t>
+  </si>
+  <si>
+    <t>2873LEON</t>
+  </si>
 </sst>
 </file>
 
@@ -30612,25 +30636,51 @@
         <v>35</v>
       </c>
       <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
+      <c r="G69" s="20" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="70" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A70" s="21"/>
-      <c r="B70" s="22"/>
-      <c r="C70" s="22"/>
-      <c r="D70" s="22"/>
-      <c r="E70" s="22"/>
+      <c r="A70" s="29">
+        <v>31495759000116</v>
+      </c>
+      <c r="B70" s="29" t="s">
+        <v>176</v>
+      </c>
+      <c r="C70" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="D70" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="E70" s="22" t="s">
+        <v>35</v>
+      </c>
       <c r="F70" s="22"/>
-      <c r="G70" s="22"/>
+      <c r="G70" s="22" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="71" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A71" s="21"/>
-      <c r="B71" s="22"/>
-      <c r="C71" s="22"/>
-      <c r="D71" s="22"/>
-      <c r="E71" s="22"/>
+      <c r="A71" s="21">
+        <v>28738688000120</v>
+      </c>
+      <c r="B71" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="C71" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="D71" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="E71" s="22" t="s">
+        <v>35</v>
+      </c>
       <c r="F71" s="22"/>
-      <c r="G71" s="22"/>
+      <c r="G71" s="22" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="72" spans="1:7" ht="15.75" customHeight="1">
       <c r="A72" s="21"/>
@@ -36513,43 +36563,85 @@
       </c>
       <c r="E70" s="22"/>
       <c r="F70" s="22"/>
-      <c r="G70" s="22"/>
+      <c r="G70" s="22" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="71" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A71" s="22"/>
-      <c r="B71" s="22"/>
-      <c r="C71" s="22"/>
-      <c r="D71" s="22"/>
+      <c r="A71" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B71" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="C71" s="22">
+        <v>31495759000116</v>
+      </c>
+      <c r="D71" s="29" t="s">
+        <v>176</v>
+      </c>
       <c r="E71" s="22"/>
       <c r="F71" s="22"/>
-      <c r="G71" s="22"/>
+      <c r="G71" s="22" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="72" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A72" s="22"/>
-      <c r="B72" s="22"/>
-      <c r="C72" s="22"/>
-      <c r="D72" s="22"/>
+      <c r="A72" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B72" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="C72" s="22">
+        <v>31495759000116</v>
+      </c>
+      <c r="D72" s="29" t="s">
+        <v>176</v>
+      </c>
       <c r="E72" s="22"/>
       <c r="F72" s="22"/>
-      <c r="G72" s="22"/>
+      <c r="G72" s="22" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="73" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A73" s="22"/>
-      <c r="B73" s="22"/>
-      <c r="C73" s="22"/>
-      <c r="D73" s="22"/>
+      <c r="A73" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B73" s="22" t="s">
+        <v>180</v>
+      </c>
+      <c r="C73" s="22">
+        <v>31495759000116</v>
+      </c>
+      <c r="D73" s="29" t="s">
+        <v>176</v>
+      </c>
       <c r="E73" s="22"/>
       <c r="F73" s="22"/>
-      <c r="G73" s="22"/>
+      <c r="G73" s="22" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="74" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A74" s="22"/>
-      <c r="B74" s="22"/>
-      <c r="C74" s="22"/>
-      <c r="D74" s="22"/>
+      <c r="A74" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B74" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="C74" s="22">
+        <v>28738688000120</v>
+      </c>
+      <c r="D74" s="22" t="s">
+        <v>182</v>
+      </c>
       <c r="E74" s="22"/>
       <c r="F74" s="22"/>
-      <c r="G74" s="22"/>
+      <c r="G74" s="22" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="75" spans="1:7" ht="15.75" customHeight="1">
       <c r="A75" s="22"/>
